--- a/admin/EDF_Purchasing_Tracker.xlsx
+++ b/admin/EDF_Purchasing_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Speed\Projects\edf-testbed\admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA180EFB-D208-486F-84B6-01297D204237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D362F9-A9D6-485C-AE5D-7A6F4083476D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -925,7 +925,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD5F0D5"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3078,7 +3085,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D48">
-    <cfRule type="expression" dxfId="1" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>$A49="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
